--- a/streamlit_deploy/truyvan_thuyvan/Lưu lượng Sản lượng Buôn Tua Srah 1977_2026.xlsx
+++ b/streamlit_deploy/truyvan_thuyvan/Lưu lượng Sản lượng Buôn Tua Srah 1977_2026.xlsx
@@ -5929,7 +5929,7 @@
         <v>37.911999999999999</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>15.9484973</v>
+        <v>32.3673739</v>
       </c>
       <c r="M52" s="8"/>
       <c r="N52" s="8"/>
@@ -5963,7 +5963,7 @@
         <v>250.98</v>
       </c>
       <c r="Z52" s="8" t="n">
-        <v>205.92</v>
+        <v>194.62</v>
       </c>
     </row>
     <row r="53" spans="2:28" ht="15" ns3:dyDescent="0.25">
